--- a/dispute case list.xlsx
+++ b/dispute case list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\airm2\dispute_case\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818FA5B2-6B4F-4F96-B1A5-5E8E0A840145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BDBBEB-1B6A-4509-9FC2-B858F4217332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1ED8E544-86CD-4887-AEC6-CD13C9D33657}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="135">
   <si>
     <t>보험</t>
   </si>
@@ -47,43 +47,386 @@
     <t>실손보험(치료비)</t>
   </si>
   <si>
+    <t>자동차보험(대인)</t>
+  </si>
+  <si>
     <t>질병·상해·간병보험(기타)</t>
   </si>
   <si>
     <t>손해보험(책임보험)</t>
   </si>
   <si>
+    <t>자동차보험(특약)</t>
+  </si>
+  <si>
+    <t>자동차내부에 빗물이 흘러 들어가서 발생한 손해에 대하여 침수 관련 자동차 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>기명피보험자의 사위나 며느리가 사실혼 관계라는 이유로 가족운전자한정 운전특약 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>자동차보험(자기차량손해)</t>
+  </si>
+  <si>
+    <t>다른 물체와의 충돌로 인한 손해에 대해 자기차량손해 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
     <t>자동차보험(대물)</t>
   </si>
   <si>
+    <t>사고로 자동차가 대부분 파손됨으로써 해지된 리스계약 위약금에 대해 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>자동차사고로 인해 파손된 자동차가 운행이 가능하다는 이유로 견인비용 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>피해 자동차가 출고 후 5년이 경과한 자동차에 해당하여 자동차시세 하락손해 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>자동차 수리비가 사고 직전 자동차시세의 20%를 초과하지 않아 자동차시세 하락손해 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>교통사고로 파손된 차량을 수리하는 기간동안 발생한 영업손해를 보험회사가 임의로 산정한 사례</t>
+  </si>
+  <si>
+    <t>교통사고로 파손된 차량을 수리하는 기간동안 사용한 렌트카 대차료를 일부만 보상받은 사례</t>
+  </si>
+  <si>
     <t>폐차한 차량에 대한 교환가액을 자동차시세 평가업체 중고시세를 적용하여 실제보다 낮게 산정된 사례</t>
   </si>
   <si>
+    <t>자동차사고로 손상된 카시트 수리비용을 자동차보험(｢대물배상｣)에서 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>자동차사고 발생에 대한 과실이 상대방보다 작은 데도 사고 상대방의 자동차 수리비 등 보험금을 지급한 사례</t>
+  </si>
+  <si>
+    <t>자동차 사고로 인한 부상을 치료하는 기간동안 휴업으로 인한 수입감소액을 보험회사가 임의로 산정한 사례</t>
+  </si>
+  <si>
+    <t>교통사고로 상해12급을 진단받고 4주가 경과하여 치료를 받는 중에 보험회사로부터 진료비 지급보증을 거절당한 사례</t>
+  </si>
+  <si>
+    <t>음주운전 사고로 인해 발생한 피해자의 손해를 보험회사가 배상하고 피보험자에게 구상한 사례</t>
+  </si>
+  <si>
+    <t>자가용 승용차로 배달 아르바이트를 하던 중 일으킨 차량 추돌사고와 관련해서 자동차보험금(｢대인배상Ⅱ｣, ｢대물배상｣)을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>손해보험(운전자)</t>
+  </si>
+  <si>
+    <t>진행 중이던 민사소송을 취하했다는 이유로 민사소송법률비용을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>교통사고 사건으로 검찰에 송치되었으나 공소가 제기되기 전에 지출한 변호사선임비용을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>교통사고처리지원금 보상한도액(1,000만원)이 아닌 실제 지급한 합의금(300만원)만 보험금으로 지급받은 사례</t>
+  </si>
+  <si>
+    <t>약식명령이 확정된 후 피해자에게 지급한 합의에 대해서 교통사고처리지원금 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>자가용으로 배달 아르바이트를 하다가 발생한 교통사고와 관련하여 교통사고처리지원금을 지급받지 못한 사례</t>
+  </si>
+  <si>
     <t>손해보험(재물보험)</t>
   </si>
   <si>
+    <t>냉장고를 옮기다가 파손하여 부담한 수리비에 대하여 ｢보증수리연장보험｣의 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
     <t>휴대폰 수리비 보험금에 대해서 자기부담금을 공제하고 지급받은 사례</t>
   </si>
   <si>
+    <t>공식수리센터가 아닌 사설 수리업체에서 휴대폰을 수리하였다는 이유로 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>손해가 발생한 사실을 입증할 만한 객관적 증빙이 없어 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>화재로 인한 대물배상보험금 산정시 내용연수 등에 따른 감가상각을 적용하여 보상한 사례</t>
+  </si>
+  <si>
+    <t>손해보험(자동차성능·상태점검)</t>
+  </si>
+  <si>
+    <t>보험회사와 제휴계약을 체결하지 않은 차량정비업소라는 이유로 ｢자동차성능･상태점검책임보험｣ 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>보험계약에서 정한 보증기간이 초과하였다는 이유로 ｢자동차성능･상태점검책임보험｣ 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>수리부위가 보증범위에 해당하지 않는다는 이유로 ｢자동차성능･상태점검책임보험｣ 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>과속 운전 중 도로에 생긴 포트홀에 의해 자동차 휠이 손상된 사고에 대해 ｢지방자치단체배상책임보험｣의 보험금을 일부만 지급받은 사례</t>
+  </si>
+  <si>
+    <t>음식물 자체가 가지고 있는 위험에 의한 사고라는 이유로 ｢음식물배상책임보험｣의 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>이용자의 사용상 부주의로 인하여 손해가 발생하였다는 이유로 ｢생산물배상책임보험｣의 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>운동경기 중 상해에 대해 운동경기의 고유한 위험 범위를 벗어나지 않았다는 이유로 ｢종합배상책임보험｣의 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>사무실 이사 과정에서 통상의 유지･보수의 범위를 넘어선 철거공사에 해당한다는 이유로 ｢시설소유관리자배상책임보험｣의 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>피해자가 가해자의 보험회사에 직접 ｢영업배상책임보험｣의 보험금을 청구하였는데 가해자의 자기부담금만큼은 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>재물에 대한 정당한 권리를 가진 사람에게 부담하는 손해라는 이유로 ｢일생생활배상책임보험｣의 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
     <t>직무수행 중 배상책임 사고가 발생하였다는 이유로 ｢가족일상생활배상책임보험｣의 보험금을 지급받지 못한 사례</t>
   </si>
   <si>
+    <t>전동킥보드 운행 중 발생한 사고에 대해 ｢일상생활배상책임보험｣의 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>전세로 살고 있는 아파트에서 발생한 누수사고에 대한 배상금에 대해 세입자가 가입한 ｢일상생활배상책임보험｣의 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>실손보험(기타)</t>
+  </si>
+  <si>
+    <t>건강검진 비용, 예방접종 비용, 진단서 발급비용에 대해 실손의료보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>실손보험(수술비)</t>
+  </si>
+  <si>
+    <t>백내장을 치료하기 위한 다초점 인공수정체 삽입 수술에 대해 실손의료보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>실손보험(약제비)</t>
+  </si>
+  <si>
+    <t>위험분담제 대상 항암제 투약 비용 중 제약회사로부터 환급받을 금액에 대하여 실손의료보험금을 지급 받지 못한 사례</t>
+  </si>
+  <si>
+    <t>성장호르몬제 비용을 모두 본인이 부담하고 청구한 실손의료보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>압박고정용 보호대 등 의료 보조기 구입비용에 대한 실손보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>피보험자가 지급한 의료비 중 본인부담상한액을 초과한 금액에 대하여 실손보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>‘비급여 주사료’에 해당하는 ‘관절강내 무릎 주사치료’에 대하여 실손보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>국민건강보험법상 비급여에 해당하는 치과 치료비에 대하여 실손의료보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>국민건강보험법상 비급여에 해당하는 한방치료비에 대하여 실손의료보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>부담보 조건으로 보험계약을 체결한 후 보험계약 청약일로부터 5년이 지난 뒤에 청구한 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>해지된 보험계약을 부활시킨 후 청구한 상해보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>의식이 없는 피보험자(보험금 청구권자)를 대신하여 가족이 청구한 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
     <t>피보험자가 수술 도중에 사망하였는데 상해사망보험금 지급 거절 후 재검토를 거쳐 지급받은 사례</t>
   </si>
   <si>
+    <t>보험계약 체결 시 고지한 직업과 실제 직업이 달랐음에도 불구하고 보험금을 지급받은 사례</t>
+  </si>
+  <si>
+    <t>투약처방은 받았으나 실제 복용은 하지 아니하여 보험계약 청약 시 고지하지 않았는데 ‘계약 전 알릴의무’위반으로 보험계약이 해지된 사례</t>
+  </si>
+  <si>
+    <t>보험설계사에게 보험가입 전 치료사실을 고지하였는데 계약 전 알릴의무 위반으로 보험계약이 해지된 사례</t>
+  </si>
+  <si>
+    <t>보험회사가 보험기간(만기)의 기준이 되는 보험 나이가 80세를 초과하였다는 이유로 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>보험기간 중 암으로 진단확정 되었으나 계약전 알릴의무 위반으로 보험계약이 해지된 이후 표적항암치료를 받았으나 표적항암치료보험금을 지급받은 사례</t>
+  </si>
+  <si>
+    <t>보험 가입 전에 진단받은 질병으로 보험가입 이후 수술을 받았으나 질병수술보험금을 지급받은 사례</t>
+  </si>
+  <si>
+    <t>질병·상해·간병보험(수술)</t>
+  </si>
+  <si>
+    <t>잔존치근을 제거하고 임플란트 시술을 받았는데 보철치료 보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>피부에 발생한 양성종양을 적출하는 수술을 받았는데 수술보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>찢어진 피부를 꿰매는 수술을 병원에서 받았는데 수술보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>심근경색 진단을 확정하기 위해 시술받은 관상동맥조영술에 대한 수술보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>안구건조증을 치료하기 위해 시술받은 IPL(Intense Pulsed Light)에 대해 수술비를 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>질병·상해·간병보험(입원)</t>
+  </si>
+  <si>
+    <t>입원보험금 지급일수 최고한도(120일)를 초과한 후 같은 질병으로 다시 입원한 기간에 대하여 입원보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>암 수술 후 항암치료 등을 받으면서 병행한 한방병원 입원에 대하여 암입원비를 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>질병·상해·간병보험(진단)</t>
+  </si>
+  <si>
+    <t>코로나19 진단에 대해 특정전염병 진단보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>단체보험 피보험자가 해당 단체에서 퇴직한 이후 진단받은 암에 대해서 진단보험금을 받지 못한 사례</t>
+  </si>
+  <si>
+    <t>보험가입 이후 한국표준질병･사인분류(KCD) 개정으로 질병의 분류기준이 변경되었으나 가입 당시 한국표준질병･사인분류에 따라 보험금을 지급받은 사례</t>
+  </si>
+  <si>
+    <t>농업작업 중에 발생한 재해로 인한 장해보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>보험가입 이후 보험약관이 개정되면서 새롭게 추가된 장해 항목에 대해서 장해보험금을 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>같은 사고로 증가된 장해율을 담보하는 보험금을 지급하면서 기(旣)지급 보험금(증가하기 전 장해율 관련 보험금)을 공제한 사례</t>
+  </si>
+  <si>
+    <t>생명보험(연금)</t>
+  </si>
+  <si>
+    <t>이미 납입한 특약보험료를 만기보험금으로 지급받지 못한 사례</t>
+  </si>
+  <si>
+    <t>연금보험계약을 체결하면서 받은 가입설계서에 기재되어 있는 수령예상배당금을 지급받지 못한 사례</t>
+  </si>
+  <si>
     <t>생명보험(사망)</t>
   </si>
   <si>
     <t>피보험자가 고의로 자신을 해친 경우인데도 이미 납입한 보험료를 지급받지 못한 사례</t>
   </si>
   <si>
+    <t>(분쟁조정사례) 가족이 운전한 자동차 사고 발생시 실제 운전자가 아닌 피보험자의 보험료가 할증된 사례</t>
+  </si>
+  <si>
+    <t>(분쟁조정사례) 말하는 기능 장해 관련 분쟁</t>
+  </si>
+  <si>
+    <t>(분쟁조정사례) 시설소유관리자배상책임보험 관련 구내치료비 특약 가입 사례</t>
+  </si>
+  <si>
+    <t xml:space="preserve">통상적으로 사용하는 자동차를 ‘다른 자동차’로 인정하지 않아 대물배상 보험금을 지급받지 못한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">자동차내부에 빗물이 흘러 들어가서 발생한 손해에 대하여 침수 관련 자동차 보험금을 지급받지 못한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">기명피보험자의 사위나 며느리가 사실혼 관계라는 이유로 가족운전자한정 운전특약 보험금을 지급받지 못한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">다른 물체와의 충돌로 인한 손해에 대해 자기차량손해 보험금을 지급받지 못한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">사고로 자동차가 대부분 파손됨으로써 해지된 리스계약 위약금에 대해 보험금을 지급받지 못한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">자동차사고로 인해 파손된 자동차가 운행이 가능하다는 이유로 견인비용 보험금을 지급받지 못한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">피해 자동차가 출고 후 5년이 경과한 자동차에 해당하여 자동차시세 하락손해 보험금을 지급받지 못한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">자동차 수리비가 사고 직전 자동차시세의 20%를 초과하지 않아 자동차시세 하락손해 보험금을 지급받지 못한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">교통사고로 파손된 차량을 수리하는 기간동안 발생한 영업손해를 보험회사가 임의로 산정한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">교통사고로 파손된 차량을 수리하는 기간동안 사용한 렌트카 대차료를 일부만 보상받은 사례 </t>
+  </si>
+  <si>
     <t xml:space="preserve">폐차한 차량에 대한 교환가액을 자동차시세 평가업체 중고시세를 적용하여 실제보다 낮게 산정된 사례 </t>
   </si>
   <si>
+    <t xml:space="preserve">자동차사고로 손상된 카시트 수리비용을 자동차보험(｢대물배상｣)에서 지급받지 못한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">자동차사고 발생에 대한 과실이 상대방보다 작은 데도 사고 상대방의 자동차 수리비 등 보험금을 지급한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">자동차 사고로 인한 부상을 치료하는 기간동안 휴업으로 인한 수입감소액을 보험회사가 임의로 산정한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">교통사고로 상해12급을 진단받고 4주가 경과하여 치료를 받는 중에 보험회사로부터 진료비 지급보증을 거절당한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">음주운전 사고로 인해 발생한 피해자의 손해를 보험회사가 배상하고 피보험자에게 구상한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">자가용 승용차로 배달 아르바이트를 하던 중 일으킨 차량 추돌사고와 관련해서 자동차보험금(｢대인배상Ⅱ｣, ｢대물배상｣)을 지급받지 못한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">진행 중이던 민사소송을 취하했다는 이유로 민사소송법률비용을 지급받지 못한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">교통사고 사건으로 검찰에 송치되었으나 공소가 제기되기 전에 지출한 변호사선임비용을 지급받지 못한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">교통사고처리지원금 보상한도액(1,000만원)이 아닌 실제 지급한 합의금(300만원)만 보험금으로 지급받은 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">약식명령이 확정된 후 피해자에게 지급한 합의에 대해서 교통사고처리지원금 보험금을 지급받지 못한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">자가용으로 배달 아르바이트를 하다가 발생한 교통사고와 관련하여 교통사고처리지원금을 지급받지 못한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">냉장고를 옮기다가 파손하여 부담한 수리비에 대하여 ｢보증수리연장보험｣의 보험금을 지급받지 못한 사례 </t>
+  </si>
+  <si>
     <t xml:space="preserve">휴대폰 수리비 보험금에 대해서 자기부담금을 공제하고 지급받은 사례 </t>
   </si>
   <si>
+    <t xml:space="preserve">공식수리센터가 아닌 사설 수리업체에서 휴대폰을 수리하였다는 이유로 보험금을 지급받지 못한 사례 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">손해가 발생한 사실을 입증할 만한 객관적 증빙이 없어 보험금을 지급받지 못한 사례 </t>
+  </si>
+  <si>
+    <t>보험 가입 전에 진단받은 질병으로 보험가입 이후 수술을 받았으나 질병수술보험금을 지급 받은 사례</t>
+  </si>
+  <si>
     <t>(분쟁조정사례) 의학적 증거가 뒷받침되지 않는 비급여 치료의 실손보험금 부지급 사례</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(분쟁조정사례) 가족이 운전한 자동차 사고 발생시 실제 운전자가 아닌 피보험자의 보험료가 할증된 사례</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(분쟁조정사례) 말하는 기능 장해 관련 분쟁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(분쟁조정사례) 시설소유관리자배상책임보험 관련 구내치료비 특약 가입 사례</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>통상적으로 사용하는 자동차를 ‘다른 자동차’로 인정하지 않아 대물배상 보험금을 지급받지 못한 사례</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -568,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C91C67A-0046-4179-AB06-E8A15D37FDF5}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.375" bestFit="1" customWidth="1"/>
@@ -582,25 +925,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>21</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -614,13 +957,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>14</v>
+        <v>123</v>
       </c>
       <c r="E2" s="3">
         <v>46038</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>14</v>
+        <v>123</v>
       </c>
       <c r="G2" s="1">
         <v>2740</v>
@@ -628,116 +971,1795 @@
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
       <c r="E3" s="3">
-        <v>46031</v>
+        <v>46038</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="G3" s="1">
-        <v>235</v>
+        <v>638</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>125</v>
       </c>
       <c r="E4" s="3">
-        <v>46031</v>
+        <v>46038</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="G4" s="1">
-        <v>210</v>
+        <v>995</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="E5" s="3">
-        <v>46031</v>
+        <v>46038</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="G5" s="1">
-        <v>410</v>
+        <v>679</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>127</v>
       </c>
       <c r="E6" s="3">
         <v>46031</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="G6" s="1">
-        <v>302</v>
+        <v>529</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
+        <v>74</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G7" s="1">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>73</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" s="1">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>72</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="1">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>71</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" s="1">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>70</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G11" s="1">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>69</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G12" s="1">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>68</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="1">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>67</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G14" s="1">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>66</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="1">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>65</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="1">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>64</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="1">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>63</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" s="1">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>62</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G19" s="1">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>61</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G20" s="1">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>60</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G21" s="1">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>59</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" s="1">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>58</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G23" s="1">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>57</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G24" s="1">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>56</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25" s="1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>55</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G26" s="1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>54</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G27" s="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>53</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G28" s="1">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>52</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G29" s="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>51</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G30" s="1">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>50</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G31" s="1">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>49</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G32" s="1">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>48</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G33" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>47</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G34" s="1">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>46</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G35" s="1">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>45</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E36" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G36" s="1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G37" s="1">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>43</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E38" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G38" s="1">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>42</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E39" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G39" s="1">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>41</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G40" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E41" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G41" s="1">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>39</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G42" s="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>38</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E43" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G43" s="1">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>37</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E44" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G44" s="1">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>36</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E45" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G45" s="1">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>35</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E46" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G46" s="1">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>34</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E47" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G47" s="1">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>33</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E48" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G48" s="1">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>32</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="D49" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G49" s="1">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>31</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G50" s="1">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>30</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G51" s="1">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>29</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E52" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G52" s="1">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>28</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G53" s="1">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>27</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E54" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G54" s="1">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>26</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E55" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G55" s="1">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>25</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E56" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G56" s="1">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>24</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G57" s="1">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>23</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E58" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G58" s="1">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>22</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E59" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G59" s="1">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>21</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E60" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G60" s="1">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>20</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E61" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G61" s="1">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>19</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E62" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G62" s="1">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>18</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E63" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G63" s="1">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>17</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E64" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G64" s="1">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>16</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E65" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G65" s="1">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>15</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E66" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G66" s="1">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>14</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E67" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G67" s="1">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>13</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E68" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G68" s="1">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>12</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E69" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G69" s="1">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>11</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E70" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G70" s="1">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
         <v>10</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="3">
-        <v>46031</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="1">
+      <c r="B71" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E71" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G71" s="1">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>9</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E72" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G72" s="1">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>8</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E73" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G73" s="1">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>7</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E74" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G74" s="1">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>6</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E75" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G75" s="1">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>5</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E76" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G76" s="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>4</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E77" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G77" s="1">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>3</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E78" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G78" s="1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>2</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E79" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G79" s="1">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>1</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E80" s="3">
+        <v>46031</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G80" s="1">
         <v>234</v>
       </c>
     </row>
@@ -746,16 +2768,162 @@
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=128&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=1" xr:uid="{661BD41F-98B2-49FA-BFB6-F88C5D8E9AEC}"/>
     <hyperlink ref="F2" r:id="rId2" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=f28ff17668504bd89acf03118f6ac046&amp;fileSn=1&amp;bbsId=" xr:uid="{89F188FE-345D-4A9F-838F-D16367ED2D82}"/>
-    <hyperlink ref="D3" r:id="rId3" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=193&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=2" xr:uid="{583EEE4D-8BF7-4FD9-92C4-B905F34EDF11}"/>
-    <hyperlink ref="F3" r:id="rId4" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=852e694cda1b47959adb90c07f5d07ad&amp;fileSn=1&amp;bbsId=" xr:uid="{DF2FCDD1-E315-4AF7-A31B-8F07A0C86294}"/>
-    <hyperlink ref="D4" r:id="rId5" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=180&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=3" xr:uid="{21B84C03-6398-45F1-B4EA-B7014C51C2EB}"/>
-    <hyperlink ref="F4" r:id="rId6" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=01cd3802530948938c817c6eb176fd62&amp;fileSn=1&amp;bbsId=" xr:uid="{49C8643D-BA8E-4918-B6C6-00CD69337200}"/>
-    <hyperlink ref="D5" r:id="rId7" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=166&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=5" xr:uid="{FB78FF5F-2DB1-4C3E-946A-C851DDB338B5}"/>
-    <hyperlink ref="F5" r:id="rId8" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=9a40508d28a945dab87ed437b41a24fc&amp;fileSn=1&amp;bbsId=" xr:uid="{07760833-9388-4EE0-A450-E4712A9B8FC2}"/>
-    <hyperlink ref="D6" r:id="rId9" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=151&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=6" xr:uid="{BC62110A-6F92-43D2-AD78-60839AB5B0EC}"/>
-    <hyperlink ref="F6" r:id="rId10" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=54a44eebc5e444559d635a9fa877f072&amp;fileSn=1&amp;bbsId=" xr:uid="{ED83FCB5-A0A1-47B6-BECC-890F44C5D153}"/>
-    <hyperlink ref="D7" r:id="rId11" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=129&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=8" xr:uid="{C28F2CFD-C5CF-4AF4-8794-FD2ADE8CCFB1}"/>
-    <hyperlink ref="F7" r:id="rId12" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=ea8e03bf4f924f568ed3b040a07a1ba6&amp;fileSn=1&amp;bbsId=" xr:uid="{D8342725-2397-4030-A8E4-F3BF66E0260A}"/>
+    <hyperlink ref="D3" r:id="rId3" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=126&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=1" xr:uid="{2FD3DAC4-07F4-4FC3-B135-439A348EB34D}"/>
+    <hyperlink ref="F3" r:id="rId4" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=477ca6e79ce349f793a52137ebad135b&amp;fileSn=1&amp;bbsId=" xr:uid="{5A0BD51A-3D4D-4C7C-8C50-D242BDCDB5FB}"/>
+    <hyperlink ref="D4" r:id="rId5" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=125&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=1" xr:uid="{C65D298E-5321-4E17-8018-5587C3371DD5}"/>
+    <hyperlink ref="F4" r:id="rId6" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=ae66a46db254485280619520ee7e57fa&amp;fileSn=1&amp;bbsId=" xr:uid="{CC569ECA-A8BC-4FA5-9B09-18066CD84182}"/>
+    <hyperlink ref="D5" r:id="rId7" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=124&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=1" xr:uid="{BFED662B-6435-430F-82A2-5E68867B3809}"/>
+    <hyperlink ref="F5" r:id="rId8" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=3637a554f454469fa5c50279db452f6b&amp;fileSn=1&amp;bbsId=" xr:uid="{4F3FB455-FD15-4C1F-BF16-79B76AA7FE40}"/>
+    <hyperlink ref="D6" r:id="rId9" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=203&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=1" xr:uid="{262DACEF-76DD-4EAE-9839-527E7A2C6AD8}"/>
+    <hyperlink ref="F6" r:id="rId10" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=a1dd8574f80f417f916dc113a2bb2dfa&amp;fileSn=1&amp;bbsId=" xr:uid="{D49B393C-599D-485D-AB38-64C948DA1CBD}"/>
+    <hyperlink ref="D7" r:id="rId11" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=202&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=1" xr:uid="{8BA72C6D-1A45-46CF-909D-C86C30F2B3D2}"/>
+    <hyperlink ref="F7" r:id="rId12" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=dd77e4e52c714cf5a638f8ddf2df4d95&amp;fileSn=1&amp;bbsId=" xr:uid="{0E22DEF3-36AE-4B72-B280-9251D9D16E35}"/>
+    <hyperlink ref="D8" r:id="rId13" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=201&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=1" xr:uid="{3EE50584-1240-4463-ACFB-176B066F6230}"/>
+    <hyperlink ref="F8" r:id="rId14" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=7546b6332ccd43a5a2344da3a54ddd4f&amp;fileSn=1&amp;bbsId=" xr:uid="{B17061EC-7F41-4C89-BCF4-F63D1A29503E}"/>
+    <hyperlink ref="D9" r:id="rId15" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=200&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=1" xr:uid="{BF3B77F5-FEE4-437D-BFD8-BEB15245C0D9}"/>
+    <hyperlink ref="F9" r:id="rId16" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=34eb2683747341d78bb079cc54641648&amp;fileSn=1&amp;bbsId=" xr:uid="{FAA29432-4AEF-4D75-A0BC-82AB53D49820}"/>
+    <hyperlink ref="D10" r:id="rId17" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=199&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=1" xr:uid="{6099A789-3816-468A-A7B8-AEE5F143C0B7}"/>
+    <hyperlink ref="F10" r:id="rId18" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=bb019657e3ce4e0d82d40dda9ff24691&amp;fileSn=1&amp;bbsId=" xr:uid="{4AD63FF1-D935-4749-B639-B031E133AFDB}"/>
+    <hyperlink ref="D11" r:id="rId19" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=198&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=1" xr:uid="{B421DAE6-51CC-4545-847E-563280AA242E}"/>
+    <hyperlink ref="F11" r:id="rId20" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=3c8400a249a84b05869a080cabb0987e&amp;fileSn=1&amp;bbsId=" xr:uid="{3136CE98-002C-4750-9DA2-D074783F99DA}"/>
+    <hyperlink ref="D12" r:id="rId21" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=197&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=2" xr:uid="{D4C9588F-9D6E-46F2-B6D3-68CF801B0B78}"/>
+    <hyperlink ref="F12" r:id="rId22" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=bc57b9f4aa164afebfcb4c27c52fedfa&amp;fileSn=1&amp;bbsId=" xr:uid="{C8308EE4-2A45-4547-AB9A-324F7253B77D}"/>
+    <hyperlink ref="D13" r:id="rId23" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=196&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=2" xr:uid="{2C9E1029-A0DE-49D9-BC6C-3400E7D98509}"/>
+    <hyperlink ref="F13" r:id="rId24" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=a44974225ddb417f8b2179dadbb69064&amp;fileSn=1&amp;bbsId=" xr:uid="{98B9EFCE-605D-446D-BA7A-CBF9C4C22AF6}"/>
+    <hyperlink ref="D14" r:id="rId25" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=195&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=2" xr:uid="{1193A84C-B351-4B60-9F9C-F8BFC19F2E4D}"/>
+    <hyperlink ref="F14" r:id="rId26" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=2ef781690c774922964c744496924270&amp;fileSn=1&amp;bbsId=" xr:uid="{BC8B3515-54BA-4468-B872-5A0DB5D69A0F}"/>
+    <hyperlink ref="D15" r:id="rId27" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=194&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=2" xr:uid="{8DFB7925-E998-4914-801A-1E062D962849}"/>
+    <hyperlink ref="F15" r:id="rId28" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=1fc969a92b0b467bbfed735ca550de35&amp;fileSn=1&amp;bbsId=" xr:uid="{38365EA1-DFFA-4586-9FBA-C8C9B07D7E4A}"/>
+    <hyperlink ref="D16" r:id="rId29" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=193&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=2" xr:uid="{583EEE4D-8BF7-4FD9-92C4-B905F34EDF11}"/>
+    <hyperlink ref="F16" r:id="rId30" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=852e694cda1b47959adb90c07f5d07ad&amp;fileSn=1&amp;bbsId=" xr:uid="{DF2FCDD1-E315-4AF7-A31B-8F07A0C86294}"/>
+    <hyperlink ref="D17" r:id="rId31" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=192&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=2" xr:uid="{FB5BC23F-D546-4562-B1D7-9B0C469B0409}"/>
+    <hyperlink ref="F17" r:id="rId32" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=46454a0974d0450992992735537e24fe&amp;fileSn=1&amp;bbsId=" xr:uid="{32A3A981-D203-4E2C-AD52-F7968CBB1B10}"/>
+    <hyperlink ref="D18" r:id="rId33" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=191&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=2" xr:uid="{82D5AD19-F9DD-475B-A9C0-8B26BE6B0A9F}"/>
+    <hyperlink ref="F18" r:id="rId34" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=ad40225d858f4384a7ca4d4c9b0a59d1&amp;fileSn=1&amp;bbsId=" xr:uid="{DE2751CD-1C4A-4A24-9C63-E6239A04D3CB}"/>
+    <hyperlink ref="D19" r:id="rId35" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=190&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=2" xr:uid="{D5FFADB2-A08B-4502-B865-610545F62BD6}"/>
+    <hyperlink ref="F19" r:id="rId36" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=f6a33c875f8746a1aa0476152cad2618&amp;fileSn=1&amp;bbsId=" xr:uid="{97B80086-F7A8-41B7-9900-7ACE253697D2}"/>
+    <hyperlink ref="D20" r:id="rId37" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=189&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=2" xr:uid="{68D245EB-8640-4671-95CE-662B524DDFA5}"/>
+    <hyperlink ref="F20" r:id="rId38" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=e5f12e1dcde2479887d4bdf1396624b1&amp;fileSn=1&amp;bbsId=" xr:uid="{FBA5E587-D26A-4549-A5F5-637C74D285AA}"/>
+    <hyperlink ref="D21" r:id="rId39" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=188&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=2" xr:uid="{0AF8FFA7-6DB8-4097-9743-034A2AAE6884}"/>
+    <hyperlink ref="F21" r:id="rId40" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=6a10c81385754897b030275ce6d5f7b4&amp;fileSn=1&amp;bbsId=" xr:uid="{77269854-CCCA-4475-AAE1-7573F11D0217}"/>
+    <hyperlink ref="D22" r:id="rId41" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=187&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=3" xr:uid="{C856B323-28C5-44AD-B3F9-56393347C304}"/>
+    <hyperlink ref="F22" r:id="rId42" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=5b0a9ba839f14a728adc597ca7498002&amp;fileSn=1&amp;bbsId=" xr:uid="{A718F150-EAB2-4D88-BE14-BAE7BD8DDA81}"/>
+    <hyperlink ref="D23" r:id="rId43" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=186&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=3" xr:uid="{299E46A9-9823-4D7A-B1F7-D4FC5C0D61E8}"/>
+    <hyperlink ref="F23" r:id="rId44" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=e279c3d3865a4ffdbde3228ef5b33168&amp;fileSn=1&amp;bbsId=" xr:uid="{C55119F6-C272-4387-BA81-38DE6A04435A}"/>
+    <hyperlink ref="D24" r:id="rId45" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=185&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=3" xr:uid="{037B3B60-EC5F-42F8-B68F-D053EDBE72EA}"/>
+    <hyperlink ref="F24" r:id="rId46" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=d5b9bc5844bc469c91736eda5bf994ea&amp;fileSn=1&amp;bbsId=" xr:uid="{8EA50739-8106-431E-A02A-A9DA6D6C558B}"/>
+    <hyperlink ref="D25" r:id="rId47" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=184&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=3" xr:uid="{8B7E05A3-4AD2-40ED-9A63-E086EB85CA61}"/>
+    <hyperlink ref="F25" r:id="rId48" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=8481053056144691be31d37377009841&amp;fileSn=1&amp;bbsId=" xr:uid="{ABD3AD82-8ACD-4278-85B4-F6E30710BC67}"/>
+    <hyperlink ref="D26" r:id="rId49" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=183&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=3" xr:uid="{C0AD549A-B8AD-461B-BA8D-3B938173B836}"/>
+    <hyperlink ref="F26" r:id="rId50" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=084d9c48fb724d39b95885e979672803&amp;fileSn=1&amp;bbsId=" xr:uid="{7D7C96E5-A9BB-4FB9-8C6C-46DC11A6C387}"/>
+    <hyperlink ref="D27" r:id="rId51" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=182&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=3" xr:uid="{CBA41705-835F-436A-B144-CC563EC34D37}"/>
+    <hyperlink ref="F27" r:id="rId52" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=067259a51884496da616d45fca97e6fe&amp;fileSn=1&amp;bbsId=" xr:uid="{9F06E0B4-FDCA-448B-98E4-4CD02B9D8057}"/>
+    <hyperlink ref="D28" r:id="rId53" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=181&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=3" xr:uid="{6310A950-24D2-4701-A98D-59770D6AA7CF}"/>
+    <hyperlink ref="F28" r:id="rId54" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=ab0f0c368edb497ca19a17edeba77d81&amp;fileSn=1&amp;bbsId=" xr:uid="{685F1D92-8E0A-4FBA-B21A-CEDEA07A703F}"/>
+    <hyperlink ref="D29" r:id="rId55" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=180&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=3" xr:uid="{21B84C03-6398-45F1-B4EA-B7014C51C2EB}"/>
+    <hyperlink ref="F29" r:id="rId56" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=01cd3802530948938c817c6eb176fd62&amp;fileSn=1&amp;bbsId=" xr:uid="{49C8643D-BA8E-4918-B6C6-00CD69337200}"/>
+    <hyperlink ref="D30" r:id="rId57" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=179&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=3" xr:uid="{8993F8E8-0BED-4076-9AE3-2B63EA5AD42A}"/>
+    <hyperlink ref="F30" r:id="rId58" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=40cdacdf73724248b06bb2e75798dcde&amp;fileSn=1&amp;bbsId=" xr:uid="{F0A1CF44-8533-4F2C-8E03-B14AAFA155BE}"/>
+    <hyperlink ref="D31" r:id="rId59" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=178&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=3" xr:uid="{47894D7E-9E41-428A-A0AB-C5DC05AF1E7F}"/>
+    <hyperlink ref="F31" r:id="rId60" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=df2b7f902ddf47adb3176a4f64637856&amp;fileSn=1&amp;bbsId=" xr:uid="{75DA21C3-62F3-47CC-B270-87D5350E5724}"/>
+    <hyperlink ref="D32" r:id="rId61" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=177&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=4" xr:uid="{EE002E8F-3C60-4FF2-8843-47C5EA9C90A0}"/>
+    <hyperlink ref="F32" r:id="rId62" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=f30f61eb70be40d79204f3eef775f02e&amp;fileSn=1&amp;bbsId=" xr:uid="{900B2EB4-B10E-47B6-8E80-116BC9CF1CDB}"/>
+    <hyperlink ref="D33" r:id="rId63" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=176&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=4" xr:uid="{E4857D81-56D5-4874-86D0-53DDEAF73335}"/>
+    <hyperlink ref="F33" r:id="rId64" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=5bdd5970ffbf40d98c8bf70d75083f32&amp;fileSn=1&amp;bbsId=" xr:uid="{41B7C0B1-9611-4E15-B1BE-98DFF2357D45}"/>
+    <hyperlink ref="D34" r:id="rId65" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=175&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=4" xr:uid="{56E76A8D-A00B-435C-A979-EB2DC7271C1B}"/>
+    <hyperlink ref="F34" r:id="rId66" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=2a55a9a7c67748db940f1a848fb328d0&amp;fileSn=1&amp;bbsId=" xr:uid="{35829C2C-BC24-42A7-A41F-9AEB92D4BE04}"/>
+    <hyperlink ref="D35" r:id="rId67" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=174&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=4" xr:uid="{22AD5924-324D-49DA-8294-A8EC0B747D26}"/>
+    <hyperlink ref="F35" r:id="rId68" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=60795a7b5f694789ad7befe5201d70ba&amp;fileSn=1&amp;bbsId=" xr:uid="{66BF10F9-7AEA-45C7-A94F-CD399E27107E}"/>
+    <hyperlink ref="D36" r:id="rId69" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=173&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=4" xr:uid="{A7409AF0-919A-498C-9410-05FE0D70D38E}"/>
+    <hyperlink ref="F36" r:id="rId70" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=2c2b09205abd424094fa859b6c880919&amp;fileSn=1&amp;bbsId=" xr:uid="{4223E7D7-F7A5-46D4-A9F2-D80439F2E181}"/>
+    <hyperlink ref="D37" r:id="rId71" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=172&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=4" xr:uid="{46DD31AE-33DF-4C9B-BE0D-491EE2AE05FB}"/>
+    <hyperlink ref="F37" r:id="rId72" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=6a8b725e7a294b849fb3280a4fd5e62e&amp;fileSn=1&amp;bbsId=" xr:uid="{5B556248-9498-4858-A06B-0E141E4FB709}"/>
+    <hyperlink ref="D38" r:id="rId73" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=171&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=4" xr:uid="{FB94A770-662D-404F-95EE-10B9F381E22C}"/>
+    <hyperlink ref="F38" r:id="rId74" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=7678dff2ced14190ad3d46cb9c578037&amp;fileSn=1&amp;bbsId=" xr:uid="{CDB1FD93-6F9B-477B-9B5E-DE0F87EA1ACA}"/>
+    <hyperlink ref="D39" r:id="rId75" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=170&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=4" xr:uid="{6DF1CA27-3D32-44FE-A403-13B636AF0743}"/>
+    <hyperlink ref="F39" r:id="rId76" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=af8ea39c87be438980dab77ea5fef090&amp;fileSn=1&amp;bbsId=" xr:uid="{B691E822-F855-4423-8DE9-E97340B18BA9}"/>
+    <hyperlink ref="D40" r:id="rId77" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=169&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=4" xr:uid="{3E09E1C0-9B98-4A66-B86C-3CB28A881FBC}"/>
+    <hyperlink ref="F40" r:id="rId78" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=3a22b056f08642fba0e62d8f5b77f582&amp;fileSn=1&amp;bbsId=" xr:uid="{C78F3AB1-1071-4AA8-8165-16CDEF1C6049}"/>
+    <hyperlink ref="D41" r:id="rId79" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=168&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=4" xr:uid="{555CE733-11A4-4EB0-88C3-5EC05F5C46C4}"/>
+    <hyperlink ref="F41" r:id="rId80" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=9ce26f1f097e4fd09c2d83d529b04c88&amp;fileSn=1&amp;bbsId=" xr:uid="{5C8D4EF3-DAD6-433E-89F0-A464A0309431}"/>
+    <hyperlink ref="D42" r:id="rId81" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=167&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=5" xr:uid="{8100261F-D525-4EDB-9BCC-85FA1FD9566B}"/>
+    <hyperlink ref="F42" r:id="rId82" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=fb70356f91454e84ac4fe1201a35e904&amp;fileSn=1&amp;bbsId=" xr:uid="{1B9567A6-766E-4F64-8265-C4CB3877B656}"/>
+    <hyperlink ref="D43" r:id="rId83" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=166&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=5" xr:uid="{FB78FF5F-2DB1-4C3E-946A-C851DDB338B5}"/>
+    <hyperlink ref="F43" r:id="rId84" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=9a40508d28a945dab87ed437b41a24fc&amp;fileSn=1&amp;bbsId=" xr:uid="{07760833-9388-4EE0-A450-E4712A9B8FC2}"/>
+    <hyperlink ref="D44" r:id="rId85" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=165&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=5" xr:uid="{9E29E4B3-5B60-42A2-8211-F524F9AFAD4F}"/>
+    <hyperlink ref="F44" r:id="rId86" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=544d5801d8ad4166ac7a7fad0d9f810b&amp;fileSn=1&amp;bbsId=" xr:uid="{FA24004D-F655-42E2-BF57-FACCAF271F33}"/>
+    <hyperlink ref="D45" r:id="rId87" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=164&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=5" xr:uid="{F3734EDF-24D3-4F1A-A4DD-663DE0CE8CF3}"/>
+    <hyperlink ref="F45" r:id="rId88" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=d42a188b95ae4c8ebcca1878117be40d&amp;fileSn=1&amp;bbsId=" xr:uid="{C4FB1B6C-89DF-48A7-A056-824A2AF13636}"/>
+    <hyperlink ref="D46" r:id="rId89" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=163&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=5" xr:uid="{B6A8B3DC-6E39-4EF9-9E7B-B18144464CF0}"/>
+    <hyperlink ref="F46" r:id="rId90" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=63dc92b875e945bda7798b6bc5d8e7a8&amp;fileSn=1&amp;bbsId=" xr:uid="{8A94E479-0EBC-4B88-8F14-B80A3835F511}"/>
+    <hyperlink ref="D47" r:id="rId91" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=162&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=5" xr:uid="{91FBCF71-582D-41B6-A3F0-CFCD7D881336}"/>
+    <hyperlink ref="F47" r:id="rId92" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=9a2ed9e4125242a09ba927ec73b8768c&amp;fileSn=1&amp;bbsId=" xr:uid="{FD13301A-181F-4635-A915-7FD4859B3DE7}"/>
+    <hyperlink ref="D48" r:id="rId93" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=161&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=5" xr:uid="{48163F8D-BBC4-40A6-A9DA-918B28804763}"/>
+    <hyperlink ref="F48" r:id="rId94" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=e0a927cc321545719b589792bc18e3df&amp;fileSn=1&amp;bbsId=" xr:uid="{35C4AF32-1917-4D59-9CF9-8BAEA4A9D1D2}"/>
+    <hyperlink ref="D49" r:id="rId95" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=160&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=5" xr:uid="{3F12D220-499C-414F-B592-831068B5CC1F}"/>
+    <hyperlink ref="F49" r:id="rId96" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=baa0ec4749484ebdaa292638440ea78e&amp;fileSn=1&amp;bbsId=" xr:uid="{54CE0C98-6B0B-407D-86F0-15B6A64FD277}"/>
+    <hyperlink ref="D50" r:id="rId97" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=159&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=5" xr:uid="{B8991EE1-4ACF-4883-BE04-E0FC5A3946F5}"/>
+    <hyperlink ref="F50" r:id="rId98" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=11cfa70dda2a4f0e981a8eac2fd40adc&amp;fileSn=1&amp;bbsId=" xr:uid="{8334415C-3AEF-4798-A00F-E5028980E3A3}"/>
+    <hyperlink ref="D51" r:id="rId99" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=158&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=5" xr:uid="{91999493-9C2F-4E32-AC0D-4FEAB2A9379D}"/>
+    <hyperlink ref="F51" r:id="rId100" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=7e660c7f82ed431caa51420e9f5a468c&amp;fileSn=1&amp;bbsId=" xr:uid="{341A3CB4-54CB-4596-96B2-314582FF467C}"/>
+    <hyperlink ref="D52" r:id="rId101" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=157&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=6" xr:uid="{3C0869D6-5C07-482C-BF1D-F8D97D2AE899}"/>
+    <hyperlink ref="F52" r:id="rId102" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=5c53e3c7a8da4ad1ae454e09a5b7d29a&amp;fileSn=1&amp;bbsId=" xr:uid="{E9CC055E-7FAC-4F04-BF08-6EB7486BAA61}"/>
+    <hyperlink ref="D53" r:id="rId103" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=156&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=6" xr:uid="{BBF6269F-E880-409E-BAB4-E44249730823}"/>
+    <hyperlink ref="F53" r:id="rId104" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=387da9b091c8401cb27dc1e02ece3c8f&amp;fileSn=1&amp;bbsId=" xr:uid="{97B5AA9D-E423-4ECF-9B95-463500F063F0}"/>
+    <hyperlink ref="D54" r:id="rId105" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=155&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=6" xr:uid="{4954C5E7-62E5-45AF-9B96-AA0B47BABBC7}"/>
+    <hyperlink ref="F54" r:id="rId106" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=f4175eb19d9d44c4a248cff1bd783b68&amp;fileSn=1&amp;bbsId=" xr:uid="{801A4173-462E-48C7-ADAD-F549C3AFB985}"/>
+    <hyperlink ref="D55" r:id="rId107" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=154&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=6" xr:uid="{1B3778CB-2E39-4CD9-8A5C-F720831E0AA4}"/>
+    <hyperlink ref="F55" r:id="rId108" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=84fb3dc49555433ca3fc6d2a74d5c945&amp;fileSn=1&amp;bbsId=" xr:uid="{030A5D02-3765-420B-B241-7BF8F682888D}"/>
+    <hyperlink ref="D56" r:id="rId109" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=153&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=6" xr:uid="{BC838751-8C6C-4C3E-9DAE-18321D5F6788}"/>
+    <hyperlink ref="F56" r:id="rId110" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=380f17ffb68a456ebcae12049141d540&amp;fileSn=1&amp;bbsId=" xr:uid="{4EB74A5D-A6FC-4082-8464-1EC8700455E9}"/>
+    <hyperlink ref="D57" r:id="rId111" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=152&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=6" xr:uid="{83A92C4C-D332-42F8-A329-A7DBC9062481}"/>
+    <hyperlink ref="F57" r:id="rId112" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=d8cf0e91ef4f4623b7e401db0679ba5c&amp;fileSn=1&amp;bbsId=" xr:uid="{BB654102-39E5-4EC6-8F48-FC9CBEE8B9EF}"/>
+    <hyperlink ref="D58" r:id="rId113" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=151&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=6" xr:uid="{BC62110A-6F92-43D2-AD78-60839AB5B0EC}"/>
+    <hyperlink ref="F58" r:id="rId114" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=54a44eebc5e444559d635a9fa877f072&amp;fileSn=1&amp;bbsId=" xr:uid="{ED83FCB5-A0A1-47B6-BECC-890F44C5D153}"/>
+    <hyperlink ref="D59" r:id="rId115" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=150&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=6" xr:uid="{18FB6FDD-F381-4D24-A4D2-C65DBC96FF58}"/>
+    <hyperlink ref="F59" r:id="rId116" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=207a137dc66f4bf18b7c95a12b1852a3&amp;fileSn=1&amp;bbsId=" xr:uid="{D0480B6A-AF3D-4A73-9D3B-9649C45B5F0F}"/>
+    <hyperlink ref="D60" r:id="rId117" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=149&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=6" xr:uid="{92C4C628-D8DA-41E1-A3D6-30BE4EB0175B}"/>
+    <hyperlink ref="F60" r:id="rId118" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=2b8a4092b5284fbfa3a89a493f2096cb&amp;fileSn=1&amp;bbsId=" xr:uid="{9DC46D14-806C-406C-A3C6-6147F946312A}"/>
+    <hyperlink ref="D61" r:id="rId119" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=148&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=6" xr:uid="{0B710207-7A8E-45CF-878D-8D874937AA69}"/>
+    <hyperlink ref="F61" r:id="rId120" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=2f1a62535b6c4108a3ceeccf37c32bed&amp;fileSn=1&amp;bbsId=" xr:uid="{DF355C5F-509A-4BCB-ACAA-9461569C2241}"/>
+    <hyperlink ref="D62" r:id="rId121" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=147&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=7" xr:uid="{3B622A3A-52C8-4CFD-98CF-C2655480DEBA}"/>
+    <hyperlink ref="F62" r:id="rId122" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=980c237363f142c9b35385b72c6104c6&amp;fileSn=1&amp;bbsId=" xr:uid="{212B8F26-63A6-4899-886E-CE13C2A1216E}"/>
+    <hyperlink ref="D63" r:id="rId123" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=146&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=7" xr:uid="{7C8153AE-BE53-4271-B531-C7739514EC2C}"/>
+    <hyperlink ref="F63" r:id="rId124" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=a886d04a7682492db8d242275c597f33&amp;fileSn=1&amp;bbsId=" xr:uid="{5FD1C006-ED7F-439B-B646-256BDED63A2D}"/>
+    <hyperlink ref="D64" r:id="rId125" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=145&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=7" xr:uid="{E11C44CE-3012-4569-A8BA-F3FA90A3A9BE}"/>
+    <hyperlink ref="F64" r:id="rId126" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=d68671b4168848bbbff0a91187fbe969&amp;fileSn=1&amp;bbsId=" xr:uid="{14011073-1AE7-45CA-9A1C-EF245EB4849B}"/>
+    <hyperlink ref="D65" r:id="rId127" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=144&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=7" xr:uid="{C7B17311-54BB-4843-9CBF-4EEDE0EABD40}"/>
+    <hyperlink ref="F65" r:id="rId128" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=bb4a8dbc216444d19192d8651ca20935&amp;fileSn=1&amp;bbsId=" xr:uid="{2182220B-F457-4450-B4C2-393E9C26C22B}"/>
+    <hyperlink ref="D66" r:id="rId129" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=143&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=7" xr:uid="{784C706E-1063-48FD-AFDD-05DDC5AFB6C2}"/>
+    <hyperlink ref="F66" r:id="rId130" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=0eef44f1ef9d436bab70431b1696a684&amp;fileSn=1&amp;bbsId=" xr:uid="{6D2A8356-7E28-4718-B4FE-D122DFB8783E}"/>
+    <hyperlink ref="D67" r:id="rId131" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=142&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=7" xr:uid="{893AA78F-AB29-4DB4-A6A9-43B4937A7496}"/>
+    <hyperlink ref="F67" r:id="rId132" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=92dae8cdc09f489d9dd3bbe018ab422d&amp;fileSn=1&amp;bbsId=" xr:uid="{F2813623-69CE-414A-9F6D-78C6C5F832A9}"/>
+    <hyperlink ref="D68" r:id="rId133" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=141&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=7" xr:uid="{17F30ABD-9B63-49CA-829E-C895C686B5BC}"/>
+    <hyperlink ref="F68" r:id="rId134" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=7e22ea8827854eb087c358ca8db78907&amp;fileSn=1&amp;bbsId=" xr:uid="{7E801FE2-7B17-4135-BB2D-C7C8408B879F}"/>
+    <hyperlink ref="D69" r:id="rId135" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=140&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=7" xr:uid="{94CB97D5-6302-43E2-8480-09215F1842B5}"/>
+    <hyperlink ref="F69" r:id="rId136" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=f63015b90d2c48599249fd7a240cdf1e&amp;fileSn=1&amp;bbsId=" xr:uid="{43ACE52F-7456-4EB9-9E0B-9969EC0C5F0F}"/>
+    <hyperlink ref="D70" r:id="rId137" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=139&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=7" xr:uid="{B3FD4453-6FE4-4692-9840-F8076F878E50}"/>
+    <hyperlink ref="F70" r:id="rId138" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=b7e6c6c1f25d41149a6f3f4d934ab833&amp;fileSn=1&amp;bbsId=" xr:uid="{811994FB-1675-4DC9-9289-EB2045287580}"/>
+    <hyperlink ref="D71" r:id="rId139" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=138&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=7" xr:uid="{AC234F39-E1AC-43E2-B6A2-0FAC4718E631}"/>
+    <hyperlink ref="F71" r:id="rId140" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=deb89b2cde80491e8dadf8a26e7358f6&amp;fileSn=1&amp;bbsId=" xr:uid="{4C338336-124D-40A8-8043-2987EA27C37C}"/>
+    <hyperlink ref="D72" r:id="rId141" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=137&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=8" xr:uid="{A727F66D-6277-4E68-95AD-BEED576FECFC}"/>
+    <hyperlink ref="F72" r:id="rId142" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=24fdd726368f4891ba85baf4f19bcaae&amp;fileSn=1&amp;bbsId=" xr:uid="{9E296D41-B191-425A-AD6E-98D5B017FF08}"/>
+    <hyperlink ref="D73" r:id="rId143" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=136&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=8" xr:uid="{AFE1DE57-AE52-496D-BB0D-459729204B16}"/>
+    <hyperlink ref="F73" r:id="rId144" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=be62864855ce40e0bed886a73ef7cd66&amp;fileSn=1&amp;bbsId=" xr:uid="{80E1019A-76F9-43C7-AAFC-5386962C8327}"/>
+    <hyperlink ref="D74" r:id="rId145" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=135&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=8" xr:uid="{E0D1760B-DF97-49BC-8111-410539901722}"/>
+    <hyperlink ref="F74" r:id="rId146" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=86cce6161c0f426ab6cf8f846caa2380&amp;fileSn=1&amp;bbsId=" xr:uid="{DC134953-87E0-4AD4-B1CA-23712D93FA1F}"/>
+    <hyperlink ref="D75" r:id="rId147" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=134&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=8" xr:uid="{7AEFB8EB-D1BC-4D18-A0F2-A795F14FE454}"/>
+    <hyperlink ref="F75" r:id="rId148" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=c81d7c970b9a48c883072b8664a1a685&amp;fileSn=1&amp;bbsId=" xr:uid="{9B7C37FD-B816-486B-A77D-F7F81DD1AD9C}"/>
+    <hyperlink ref="D76" r:id="rId149" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=133&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=8" xr:uid="{159695E5-76C1-445A-94EB-0FD7F2431BDC}"/>
+    <hyperlink ref="F76" r:id="rId150" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=d4da28af4aed4e8f96d70595ccb11a3a&amp;fileSn=1&amp;bbsId=" xr:uid="{E26A1EBB-B991-4A72-BF26-34A4F817FFBC}"/>
+    <hyperlink ref="D77" r:id="rId151" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=132&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=8" xr:uid="{E4A4418B-CBAE-40E3-98DB-652A93F1B370}"/>
+    <hyperlink ref="F77" r:id="rId152" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=875ba4fc29bf453b868695120e8aac6c&amp;fileSn=1&amp;bbsId=" xr:uid="{DE9A3CCC-2B8C-48F4-B51D-1AFCEE6C29BD}"/>
+    <hyperlink ref="D78" r:id="rId153" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=131&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=8" xr:uid="{1583E6FC-587E-4527-9331-375D45DCAAAC}"/>
+    <hyperlink ref="F78" r:id="rId154" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=daf6500183dc49ce8ea7e43fde926f1b&amp;fileSn=1&amp;bbsId=" xr:uid="{3296524F-48FF-4EB5-AB37-AA654426ED99}"/>
+    <hyperlink ref="D79" r:id="rId155" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=130&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=8" xr:uid="{F5BA998D-3E17-4528-884C-915103EFAB01}"/>
+    <hyperlink ref="F79" r:id="rId156" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=004e6527f81a4820bfb22a8dabb5d2a1&amp;fileSn=1&amp;bbsId=" xr:uid="{0B709C2B-0F97-4D69-A44A-14C9265E5D2F}"/>
+    <hyperlink ref="D80" r:id="rId157" display="https://www.fss.or.kr/fss/job/fncCnflCase/view.do?caseSlno=129&amp;menuNo=200516&amp;searchCnd=1&amp;sdate=2026-01-01&amp;edate=2026-04-17&amp;rgnlCode=&amp;cvplCode=&amp;searchWrd=&amp;pageIndex=8" xr:uid="{C28F2CFD-C5CF-4AF4-8794-FD2ADE8CCFB1}"/>
+    <hyperlink ref="F80" r:id="rId158" display="https://www.fss.or.kr/fss/cmmn/file/fileDown.do?menuNo=200516&amp;atchFileId=ea8e03bf4f924f568ed3b040a07a1ba6&amp;fileSn=1&amp;bbsId=" xr:uid="{D8342725-2397-4030-A8E4-F3BF66E0260A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
